--- a/audit variables codebook.xlsx
+++ b/audit variables codebook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cdocuments\GitHub\labor_audit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\labor_audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C660D3A-6435-4F73-9610-C6D64FDE1C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C16DA75-B596-4986-AC1F-9EAB6A25F46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="16395" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="code book" sheetId="1" r:id="rId1"/>
@@ -328,135 +328,136 @@
     <t>accidentinvesti</t>
   </si>
   <si>
+    <t>accohs</t>
+  </si>
+  <si>
+    <t>Does the employer adequately assign accountability to management for carrying out OSH responsibilities?</t>
+  </si>
+  <si>
+    <t>impleosh</t>
+  </si>
+  <si>
+    <t>Does the employer adequately communicate and implement OSH policies and procedures?</t>
+  </si>
+  <si>
+    <t>invstiosh</t>
+  </si>
+  <si>
+    <t>Does the employer adequately investigate, monitor and measure OSH issues to identify root causes and make necessary adjustments?</t>
+  </si>
+  <si>
+    <t>variable name</t>
+  </si>
+  <si>
+    <t>original questions</t>
+  </si>
+  <si>
+    <t>has the employer elaborated and implemented an emergency plan?</t>
+  </si>
+  <si>
+    <t>Does the employer has a written emergency preparedness procedure?</t>
+  </si>
+  <si>
+    <t>similar question2</t>
+  </si>
+  <si>
+    <t>similar question3</t>
+  </si>
+  <si>
+    <t>mngsum13items</t>
+  </si>
+  <si>
+    <t>the sum of 1 or 0 answer to 13 items; system delected observations with missing value for any of the 13 items</t>
+  </si>
+  <si>
+    <t>mngitems</t>
+  </si>
+  <si>
+    <t>the number of management system items that do not include missing values. E.g. 0 would mean all are missing and 7 would mean 7 items have full values for each of the 13 items.</t>
+  </si>
+  <si>
+    <t>recruitment</t>
+  </si>
+  <si>
+    <t>"signed"; or "HR policy"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> grievance handling; or  dispute resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> communicate and implement ; or  implement HR</t>
+  </si>
+  <si>
+    <t>emergency; or  emergency preparedness</t>
+  </si>
+  <si>
+    <t>risk management</t>
+  </si>
+  <si>
+    <t>potential key terms</t>
+  </si>
+  <si>
+    <t>accountability (but check for HR only); or"following HR policies"; or "following factory policies and procedures" (check for HR only)</t>
+  </si>
+  <si>
+    <t>investigate (but check for HR); or "evaluate performance of HR"; or "HR policies and procedures to identify weaknesses"</t>
+  </si>
+  <si>
+    <t>investigate; or "accident investigation"</t>
+  </si>
+  <si>
+    <t>accountability (but check for OSH only);or "for carrying out"</t>
+  </si>
+  <si>
+    <t>Does the employer assign accountability at all levels of management for carrying out health and safety responsibilities?</t>
+  </si>
+  <si>
+    <t>implement OSH; or "OSH policies"</t>
+  </si>
+  <si>
+    <t>investigate; or "measure OSH issues"</t>
+  </si>
+  <si>
+    <t>disciplinary and termination</t>
+  </si>
+  <si>
+    <t>buyer1FTindex</t>
+  </si>
+  <si>
+    <t>buyer2FTindex</t>
+  </si>
+  <si>
+    <t>the Fashion Transparency Index (FTI) of buyer 1; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
+  </si>
+  <si>
+    <t>the Fashion Transparency Index (FTI) of buyer 2; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
+  </si>
+  <si>
+    <t>the Fashion Transparency Index (FTI) of buyer 3; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
+  </si>
+  <si>
+    <t>buyer3FTindex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTI ranked 150 fashion brands in 2018. But our data has 870 unique buyer names in total and 371 names for the first buyer. </t>
+  </si>
+  <si>
+    <t>definition or operation</t>
+  </si>
+  <si>
     <t>Is there an adequate accident investigation procedure?</t>
-  </si>
-  <si>
-    <t>accohs</t>
-  </si>
-  <si>
-    <t>Does the employer adequately assign accountability to management for carrying out OSH responsibilities?</t>
-  </si>
-  <si>
-    <t>impleosh</t>
-  </si>
-  <si>
-    <t>Does the employer adequately communicate and implement OSH policies and procedures?</t>
-  </si>
-  <si>
-    <t>invstiosh</t>
-  </si>
-  <si>
-    <t>Does the employer adequately investigate, monitor and measure OSH issues to identify root causes and make necessary adjustments?</t>
-  </si>
-  <si>
-    <t>variable name</t>
-  </si>
-  <si>
-    <t>original questions</t>
-  </si>
-  <si>
-    <t>has the employer elaborated and implemented an emergency plan?</t>
-  </si>
-  <si>
-    <t>Does the employer has a written emergency preparedness procedure?</t>
-  </si>
-  <si>
-    <t>similar question2</t>
-  </si>
-  <si>
-    <t>similar question3</t>
-  </si>
-  <si>
-    <t>mngsum13items</t>
-  </si>
-  <si>
-    <t>the sum of 1 or 0 answer to 13 items; system delected observations with missing value for any of the 13 items</t>
-  </si>
-  <si>
-    <t>mngitems</t>
-  </si>
-  <si>
-    <t>the number of management system items that do not include missing values. E.g. 0 would mean all are missing and 7 would mean 7 items have full values for each of the 13 items.</t>
-  </si>
-  <si>
-    <t>recruitment</t>
-  </si>
-  <si>
-    <t>"signed"; or "HR policy"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> grievance handling; or  dispute resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> communicate and implement ; or  implement HR</t>
-  </si>
-  <si>
-    <t>emergency; or  emergency preparedness</t>
-  </si>
-  <si>
-    <t>risk management</t>
-  </si>
-  <si>
-    <t>potential key terms</t>
-  </si>
-  <si>
-    <t>accountability (but check for HR only); or"following HR policies"; or "following factory policies and procedures" (check for HR only)</t>
-  </si>
-  <si>
-    <t>investigate (but check for HR); or "evaluate performance of HR"; or "HR policies and procedures to identify weaknesses"</t>
-  </si>
-  <si>
-    <t>investigate; or "accident investigation"</t>
-  </si>
-  <si>
-    <t>accountability (but check for OSH only);or "for carrying out"</t>
-  </si>
-  <si>
-    <t>Does the employer assign accountability at all levels of management for carrying out health and safety responsibilities?</t>
-  </si>
-  <si>
-    <t>implement OSH; or "OSH policies"</t>
-  </si>
-  <si>
-    <t>investigate; or "measure OSH issues"</t>
-  </si>
-  <si>
-    <t>disciplinary and termination</t>
-  </si>
-  <si>
-    <t>buyer1FTindex</t>
-  </si>
-  <si>
-    <t>buyer2FTindex</t>
-  </si>
-  <si>
-    <t>the Fashion Transparency Index (FTI) of buyer 1; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
-  </si>
-  <si>
-    <t>the Fashion Transparency Index (FTI) of buyer 2; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
-  </si>
-  <si>
-    <t>the Fashion Transparency Index (FTI) of buyer 3; it is coded as "-1" for those buyers that are not ranked by FTI; "-2" for those factories whose buyer names are missing.</t>
-  </si>
-  <si>
-    <t>buyer3FTindex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTI ranked 150 fashion brands in 2018. But our data has 870 unique buyer names in total and 371 names for the first buyer. </t>
-  </si>
-  <si>
-    <t>definition or operation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -464,15 +465,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -790,21 +798,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="77.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -812,7 +820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -820,7 +828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -828,7 +836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -836,7 +844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -844,7 +852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -852,7 +860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -860,7 +868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -868,7 +876,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -876,7 +884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -884,7 +892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -892,7 +900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -900,7 +908,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -908,7 +916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -916,7 +924,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -924,7 +932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -932,7 +940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -940,7 +948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -948,7 +956,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -956,7 +964,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -964,7 +972,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -972,7 +980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -980,7 +988,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -988,7 +996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -996,7 +1004,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1004,7 +1012,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1012,7 +1020,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1020,7 +1028,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1028,7 +1036,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1036,7 +1044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1044,7 +1052,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -1052,7 +1060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1060,7 +1068,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -1068,7 +1076,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -1076,7 +1084,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -1084,7 +1092,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -1092,7 +1100,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -1100,7 +1108,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -1108,7 +1116,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -1116,68 +1124,70 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>133</v>
       </c>
-      <c r="C43" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" t="s">
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" t="s">
-        <v>135</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055C5207-483C-47F2-9B33-4BD985FA48B1}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="13.59765625" customWidth="1"/>
-    <col min="3" max="3" width="75.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.1328125" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" customWidth="1"/>
+    <col min="1" max="1" width="14.9296875" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="149.59765625" customWidth="1"/>
+    <col min="4" max="4" width="110.9296875" customWidth="1"/>
+    <col min="5" max="5" width="50.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>79</v>
       </c>
@@ -1188,10 +1198,10 @@
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="3"/>
       <c r="B3" t="s">
         <v>82</v>
@@ -1200,10 +1210,10 @@
         <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>84</v>
@@ -1212,10 +1222,10 @@
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="3"/>
       <c r="B5" t="s">
         <v>86</v>
@@ -1224,10 +1234,10 @@
         <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="3"/>
       <c r="B6" t="s">
         <v>88</v>
@@ -1236,10 +1246,10 @@
         <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>90</v>
@@ -1248,10 +1258,10 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3"/>
       <c r="B8" t="s">
         <v>92</v>
@@ -1260,10 +1270,10 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="3"/>
       <c r="B9" t="s">
         <v>94</v>
@@ -1272,16 +1282,16 @@
         <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" t="s">
         <v>108</v>
       </c>
-      <c r="F9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="3"/>
       <c r="B10" t="s">
         <v>96</v>
@@ -1290,74 +1300,74 @@
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="3"/>
       <c r="B11" t="s">
         <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="3"/>
       <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
         <v>100</v>
       </c>
-      <c r="C12" t="s">
-        <v>101</v>
-      </c>
       <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
         <v>126</v>
       </c>
-      <c r="E12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="3"/>
       <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
         <v>102</v>
       </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
       <c r="D13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="3"/>
       <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
         <v>104</v>
       </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
       <c r="D14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
         <v>112</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="2" t="s">
+      <c r="C17" t="s">
         <v>114</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1365,6 +1375,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:A14"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>